--- a/DB.xlsx
+++ b/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sandvik-my.sharepoint.com/personal/erdogan_orhan_walter-tools_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFBD8A8D-DC80-4EDF-A107-93665323DB12}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15478A33-1293-47C6-A168-B7F00D2D1AC5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1BF7449C-B9C7-49F5-BC75-D9F2737E474B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="203">
   <si>
     <t>SAP</t>
   </si>
@@ -642,6 +642,15 @@
   </si>
   <si>
     <t>100338 298957 603382 605610</t>
+  </si>
+  <si>
+    <t>ALTERNATİF SAP</t>
+  </si>
+  <si>
+    <t>294087 294408 298628 298968 299552 602064 605025 605694</t>
+  </si>
+  <si>
+    <t>YENİ ALTERNATIF</t>
   </si>
 </sst>
 </file>
@@ -1057,2012 +1066,2547 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D121BD-79E7-4CC0-A08F-DA97CDCC98A5}">
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:D262"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="192.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="23.5546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="203.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>5398795</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2">
+        <v>8613735</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>7243868</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>7310123</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>6680174</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>7243904</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5652820</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7269368</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8016825</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8026019</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2"/>
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>7425489</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>6907637</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>6961081</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2"/>
+      <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>7269365</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>6634856</v>
       </c>
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>7105384</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>6682298</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>7366785</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>7105386</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>5398702</v>
       </c>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>8613347</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>5834790</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2"/>
+      <c r="C21" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>8012950</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2"/>
+      <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>7901960</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>5691048</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>7244726</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2"/>
+      <c r="C25" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>6686663</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>5856728</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2"/>
+      <c r="C27" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>7316495</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2"/>
+      <c r="C28" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>6902777</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2"/>
+      <c r="C29" s="3">
         <v>609018</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>6685094</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2"/>
+      <c r="C30" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>7275278</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2"/>
+      <c r="C31" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>5073591</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2"/>
+      <c r="C32" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>7269390</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>6015377</v>
       </c>
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>8214258</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2"/>
+      <c r="C35" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>6683830</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2"/>
+      <c r="C36" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>5834800</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2"/>
+      <c r="C37" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>7246592</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2"/>
+      <c r="C38" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>7242705</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2"/>
+      <c r="C39" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>6901527</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2"/>
+      <c r="C40" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>8016824</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2"/>
+      <c r="C41" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D41" s="3"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>5834802</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2"/>
+      <c r="C42" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>6015413</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="2"/>
+      <c r="C43" s="3">
         <v>393788</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>6692717</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2"/>
+      <c r="C44" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D44" s="3"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>5398789</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="2"/>
+      <c r="C45" s="3">
         <v>603144</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>7041014</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2"/>
+      <c r="C46" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D46" s="3"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>8186984</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2"/>
+      <c r="C47" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D47" s="3"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>6634867</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="2"/>
+      <c r="C48" s="3">
         <v>294642</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>6685097</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2"/>
+      <c r="C49" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>7144515</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2"/>
+      <c r="C50" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>7372454</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2"/>
+      <c r="C51" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D51" s="3"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>5337007</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2"/>
+      <c r="C52" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D52" s="3"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>7374102</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2"/>
+      <c r="C53" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D53" s="3"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>5398633</v>
       </c>
-      <c r="B54" s="3"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B54" s="2"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>6680148</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2"/>
+      <c r="C55" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D55" s="3"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>5850286</v>
       </c>
-      <c r="B56" s="3"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B56" s="2"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>5643787</v>
       </c>
-      <c r="B57" s="3"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B57" s="2"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>5398751</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2"/>
+      <c r="C58" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D58" s="3"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>8061089</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2"/>
+      <c r="C59" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D59" s="3"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>6686644</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2"/>
+      <c r="C60" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>6839957</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2"/>
+      <c r="C61" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D61" s="3"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>6634869</v>
       </c>
-      <c r="B62" s="3"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B62" s="2">
+        <v>8608789</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>7213124</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2"/>
+      <c r="C63" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D63" s="3"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>7246598</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2"/>
+      <c r="C64" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D64" s="3"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>7536008</v>
       </c>
-      <c r="B65" s="3"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B65" s="2"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>5834809</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2"/>
+      <c r="C66" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D66" s="3"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>5609163</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2"/>
+      <c r="C67" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D67" s="3"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>5835439</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2"/>
+      <c r="C68" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D68" s="3"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>5874343</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2"/>
+      <c r="C69" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D69" s="3"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>6683829</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2"/>
+      <c r="C70" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D70" s="3"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>6541400</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2"/>
+      <c r="C71" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D71" s="3"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>6536188</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="2"/>
+      <c r="C72" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D72" s="5"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>6972450</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2"/>
+      <c r="C73" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D73" s="3"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>6541368</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2"/>
+      <c r="C74" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D74" s="3"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>7316473</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2"/>
+      <c r="C75" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D75" s="3"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>5834792</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2"/>
+      <c r="C76" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D76" s="3"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>7032027</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2"/>
+      <c r="C77" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D77" s="3"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>6541367</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2"/>
+      <c r="C78" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D78" s="3"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>6554983</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2"/>
+      <c r="C79" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D79" s="3"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>7268757</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="2"/>
+      <c r="C80" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>7246472</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2"/>
+      <c r="C81" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D81" s="3"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>6692733</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2"/>
+      <c r="C82" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>5915595</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2"/>
+      <c r="C83" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D83" s="3"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>6316126</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2"/>
+      <c r="C84" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D84" s="3"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>6685095</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="2"/>
+      <c r="C85" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D85" s="4"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>6636195</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2"/>
+      <c r="C86" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D86" s="3"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>7243866</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2"/>
+      <c r="C87" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D87" s="3"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>6636198</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2"/>
+      <c r="C88" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D88" s="3"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>6435653</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2"/>
+      <c r="C89" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D89" s="3"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>6574396</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2"/>
+      <c r="C90" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D90" s="3"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>5564866</v>
       </c>
-      <c r="B91" s="3"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B91" s="2"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>5564911</v>
       </c>
-      <c r="B92" s="3"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B92" s="2"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>8221622</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2"/>
+      <c r="C93" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D93" s="3"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>7515113</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2"/>
+      <c r="C94" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D94" s="3"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>5200217</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2"/>
+      <c r="C95" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>7684289</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2"/>
+      <c r="C96" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D96" s="3"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>6574415</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="2"/>
+      <c r="C97" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D97" s="5"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>5603552</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2"/>
+      <c r="C98" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>5564868</v>
       </c>
       <c r="B99" s="2"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>6574417</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2"/>
+      <c r="C100" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D100" s="3"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>6026925</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2"/>
+      <c r="C101" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D101" s="3"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>6026926</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2"/>
+      <c r="C102" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D102" s="3"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>6054307</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="2"/>
+      <c r="C103" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D103" s="5"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>6054279</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="2"/>
+      <c r="C104" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D104" s="2"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>5564922</v>
       </c>
-      <c r="B105" s="3"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B105" s="2"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>5564912</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2"/>
+      <c r="C106" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D106" s="3"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>5564919</v>
       </c>
-      <c r="B107" s="3"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B107" s="2"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>5932217</v>
       </c>
-      <c r="B108" s="3"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B108" s="2"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>6588365</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2"/>
+      <c r="C109" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D109" s="3"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>8214167</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2"/>
+      <c r="C110" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D110" s="3"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>6821040</v>
       </c>
-      <c r="B111" s="3">
+      <c r="B111" s="2"/>
+      <c r="C111" s="3">
         <v>605333</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D111" s="3"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>6323863</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2"/>
+      <c r="C112" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D112" s="3"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>6792124</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2"/>
+      <c r="C113" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D113" s="3"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>5930639</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2"/>
+      <c r="C114" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D114" s="3"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>5930622</v>
       </c>
-      <c r="B115" s="5"/>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B115" s="2"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>6313621</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2"/>
+      <c r="C116" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D116" s="3"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>5404935</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2"/>
+      <c r="C117" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D117" s="3"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>6636194</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="2"/>
+      <c r="C118" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D118" s="5"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>6636192</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2"/>
+      <c r="C119" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D119" s="3"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>6819875</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2"/>
+      <c r="C120" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D120" s="3"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>6822509</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2"/>
+      <c r="C121" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D121" s="3"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>7425487</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2"/>
+      <c r="C122" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D122" s="3"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>5834665</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2"/>
+      <c r="C123" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D123" s="3"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>6763436</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2"/>
+      <c r="C124" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D124" s="3"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>6680179</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2"/>
+      <c r="C125" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D125" s="3"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>6977872</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2"/>
+      <c r="C126" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D126" s="3"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>6962850</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2"/>
+      <c r="C127" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D127" s="3"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>6373052</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2"/>
+      <c r="C128" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D128" s="3"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>7269201</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="2"/>
+      <c r="C129" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>6026025</v>
       </c>
-      <c r="B130" s="3"/>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B130" s="2"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>5834099</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131" s="2"/>
+      <c r="C131" s="3">
         <v>605407</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D131" s="3"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>5150521</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132" s="2"/>
+      <c r="C132" s="3">
         <v>605410</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D132" s="3"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>7172799</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2"/>
+      <c r="C133" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D133" s="3"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>6907148</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2"/>
+      <c r="C134" s="3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D134" s="3"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>6432502</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2"/>
+      <c r="C135" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D135" s="3"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>5093169</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2"/>
+      <c r="C136" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D136" s="3"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>6543443</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2"/>
+      <c r="C137" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D137" s="3"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>6682599</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2"/>
+      <c r="C138" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D138" s="3"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>8214176</v>
       </c>
-      <c r="B139" s="3"/>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B139" s="2"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>6960754</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2"/>
+      <c r="C140" s="3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D140" s="3"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>6574414</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2"/>
+      <c r="C141" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D141" s="3"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>7909605</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2"/>
+      <c r="C142" s="3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D142" s="3"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>7243905</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2"/>
+      <c r="C143" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D143" s="3"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>6819874</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2"/>
+      <c r="C144" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D144" s="3"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>6026028</v>
       </c>
-      <c r="B145" s="3"/>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="2"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>6822504</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2"/>
+      <c r="C146" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D146" s="3"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>7242680</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2"/>
+      <c r="C147" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D147" s="3"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>6745480</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2"/>
+      <c r="C148" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D148" s="3"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>7377485</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="2"/>
+      <c r="C149" s="3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D149" s="3"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>6432550</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="2"/>
+      <c r="C150" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D150" s="3"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>7559572</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2"/>
+      <c r="C151" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D151" s="3"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>7559571</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="2"/>
+      <c r="C152" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D152" s="3"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>7559570</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2"/>
+      <c r="C153" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D153" s="3"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>5119525</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="2"/>
+      <c r="C154" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D154" s="3"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>7389027</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2"/>
+      <c r="C155" s="3" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D155" s="3"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>8088591</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2"/>
+      <c r="C156" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D156" s="3"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>5564929</v>
       </c>
-      <c r="B157" s="3"/>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="2"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>5924822</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2"/>
+      <c r="C158" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D158" s="3"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>6149840</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2"/>
+      <c r="C159" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D159" s="3"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>7684336</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2"/>
+      <c r="C160" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D160" s="3"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>5290055</v>
       </c>
-      <c r="B161" s="3"/>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="2"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>5564915</v>
       </c>
-      <c r="B162" s="3"/>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="2"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>7242681</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2"/>
+      <c r="C163" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D163" s="3"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>5930623</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2"/>
+      <c r="C164" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D164" s="3"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>8012457</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2"/>
+      <c r="C165" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>6245534</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2"/>
+      <c r="C166" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D166" s="3"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>5650559</v>
       </c>
-      <c r="B167" s="3"/>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="2"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>5432650</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2"/>
+      <c r="C168" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D168" s="3"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>6907677</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2"/>
+      <c r="C169" s="3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D169" s="3"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>5649938</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="2"/>
+      <c r="C170" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D170" s="3"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>6054309</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2"/>
+      <c r="C171" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D171" s="3"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>6015253</v>
       </c>
-      <c r="B172" s="3"/>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="2"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>6541365</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2"/>
+      <c r="C173" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D173" s="3"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>7310128</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2"/>
+      <c r="C174" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D174" s="3"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>5337002</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2"/>
+      <c r="C175" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D175" s="3"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>5855768</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2"/>
+      <c r="C176" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D176" s="3"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>6541364</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="2"/>
+      <c r="C177" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D177" s="3"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>6680172</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2"/>
+      <c r="C178" s="3" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D178" s="3"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>6577989</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2"/>
+      <c r="C179" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D179" s="3"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>7269364</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2"/>
+      <c r="C180" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D180" s="3"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>6907286</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="2"/>
+      <c r="C181" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D181" s="3"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>6502447</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2"/>
+      <c r="C182" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D182" s="3"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>6686640</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2"/>
+      <c r="C183" s="3" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D183" s="3"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>5835437</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="2"/>
+      <c r="C184" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D184" s="3"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>5431642</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2"/>
+      <c r="C185" s="3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D185" s="3"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>6686538</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2"/>
+      <c r="C186" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D186" s="3"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>7941890</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2"/>
+      <c r="C187" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D187" s="3"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>6686561</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2"/>
+      <c r="C188" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D188" s="3"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>6686531</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="2"/>
+      <c r="C189" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D189" s="3"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>8013503</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="2"/>
+      <c r="C190" s="3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D190" s="3"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>6323847</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="2"/>
+      <c r="C191" s="3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D191" s="3"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>6536180</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="2"/>
+      <c r="C192" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D192" s="3"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>5965000</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="2"/>
+      <c r="C193" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D193" s="3"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>6846123</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="2"/>
+      <c r="C194" s="3" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D194" s="3"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>6634853</v>
       </c>
-      <c r="B195" s="3"/>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B195" s="2"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>6962853</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="2"/>
+      <c r="C196" s="3" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D196" s="3"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>6634852</v>
       </c>
-      <c r="B197" s="3"/>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B197" s="2"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>8199074</v>
       </c>
-      <c r="B198" s="3"/>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B198" s="2"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>7372458</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="2"/>
+      <c r="C199" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D199" s="3"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>5042239</v>
       </c>
-      <c r="B200" s="3"/>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B200" s="2"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>5042188</v>
       </c>
-      <c r="B201" s="3"/>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B201" s="2"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>5042204</v>
       </c>
-      <c r="B202" s="3"/>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B202" s="2"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>8115583</v>
       </c>
-      <c r="B203" s="3"/>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B203" s="2"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>8115964</v>
       </c>
-      <c r="B204" s="3"/>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B204" s="2"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>8115759</v>
       </c>
-      <c r="B205" s="3"/>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="2"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>8115949</v>
       </c>
-      <c r="B206" s="3"/>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B206" s="2"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>8199067</v>
       </c>
-      <c r="B207" s="3">
+      <c r="B207" s="2"/>
+      <c r="C207" s="3">
         <v>603084</v>
       </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D207" s="3"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>8199070</v>
       </c>
-      <c r="B208" s="3"/>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B208" s="2"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>8199073</v>
       </c>
-      <c r="B209" s="3">
+      <c r="B209" s="2"/>
+      <c r="C209" s="3">
         <v>604132</v>
       </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D209" s="3"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>6913048</v>
       </c>
-      <c r="B210" s="3"/>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B210" s="2"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>8204204</v>
       </c>
-      <c r="B211" s="3"/>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B211" s="2"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>6791676</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="2"/>
+      <c r="C212" s="3" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D212" s="3"/>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>7534743</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="2"/>
+      <c r="C213" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D213" s="3"/>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>8201083</v>
       </c>
-      <c r="B214" s="3"/>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B214" s="2"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>8296381</v>
       </c>
-      <c r="B215" s="3"/>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B215" s="2"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>6863847</v>
       </c>
-      <c r="B216" s="3"/>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B216" s="2"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>6171424</v>
       </c>
-      <c r="B217" s="3"/>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B217" s="2"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>7968917</v>
       </c>
-      <c r="B218" s="3"/>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B218" s="2"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>7969064</v>
       </c>
-      <c r="B219" s="3"/>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B219" s="2"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>7969106</v>
       </c>
-      <c r="B220" s="3"/>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B220" s="2"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>7566649</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="2"/>
+      <c r="C221" s="3" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D221" s="3"/>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>7969105</v>
       </c>
-      <c r="B222" s="3"/>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B222" s="2"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>7169820</v>
       </c>
-      <c r="B223" s="3"/>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B223" s="2"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>8325013</v>
       </c>
-      <c r="B224" s="3"/>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B224" s="2"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>8324993</v>
       </c>
-      <c r="B225" s="3"/>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B225" s="2"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="3"/>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>7696085</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="2"/>
+      <c r="C226" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D226" s="3"/>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>5904483</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="2"/>
+      <c r="C227" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D227" s="3"/>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>7246479</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="2"/>
+      <c r="C228" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D228" s="3"/>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>5398643</v>
       </c>
-      <c r="B229" s="3">
+      <c r="B229" s="2"/>
+      <c r="C229" s="3">
         <v>605171</v>
       </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D229" s="3"/>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>7246576</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="2"/>
+      <c r="C230" s="3" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D230" s="3"/>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>7073348</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="2"/>
+      <c r="C231" s="3" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D231" s="3"/>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>8364176</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="2"/>
+      <c r="C232" s="3" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D232" s="3"/>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>6577995</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B233" s="2"/>
+      <c r="C233" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D233" s="3"/>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>5398718</v>
       </c>
-      <c r="B234" s="3"/>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B234" s="2"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>8184829</v>
       </c>
-      <c r="B235" s="3" t="s">
+      <c r="B235" s="2"/>
+      <c r="C235" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D235" s="3"/>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>6808518</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B236" s="2"/>
+      <c r="C236" s="3" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D236" s="3"/>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>6907673</v>
       </c>
-      <c r="B237" s="3" t="s">
+      <c r="B237" s="2"/>
+      <c r="C237" s="3" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="238" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D237" s="3"/>
+    </row>
+    <row r="238" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>7577888</v>
       </c>
-      <c r="B238" s="3" t="s">
+      <c r="B238" s="2"/>
+      <c r="C238" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D238" s="3"/>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>6105203</v>
       </c>
-      <c r="B239" s="3"/>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B239" s="2"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>8026040</v>
       </c>
-      <c r="B240" s="3" t="s">
+      <c r="B240" s="2"/>
+      <c r="C240" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D240" s="3"/>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>6588369</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B241" s="2"/>
+      <c r="C241" s="3" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D241" s="3"/>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>5398805</v>
       </c>
-      <c r="B242" s="3" t="s">
+      <c r="B242" s="2"/>
+      <c r="C242" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D242" s="3"/>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>5932226</v>
       </c>
-      <c r="B243" s="3"/>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B243" s="2"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>6967901</v>
       </c>
-      <c r="B244" s="3">
+      <c r="B244" s="2"/>
+      <c r="C244" s="3">
         <v>602745</v>
       </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D244" s="3"/>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>6428234</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B245" s="2"/>
+      <c r="C245" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D245" s="3"/>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>6680170</v>
       </c>
-      <c r="B246" s="3" t="s">
+      <c r="B246" s="2"/>
+      <c r="C246" s="3" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D246" s="3"/>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>5337020</v>
       </c>
-      <c r="B247" s="3" t="s">
+      <c r="B247" s="2"/>
+      <c r="C247" s="3" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D247" s="3"/>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>7243901</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B248" s="2"/>
+      <c r="C248" s="3" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D248" s="3"/>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>6577997</v>
       </c>
-      <c r="B249" s="3" t="s">
+      <c r="B249" s="2"/>
+      <c r="C249" s="3" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D249" s="3"/>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
         <v>6907269</v>
       </c>
-      <c r="B250" s="3" t="s">
+      <c r="B250" s="2"/>
+      <c r="C250" s="3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D250" s="3"/>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
         <v>5536105</v>
       </c>
-      <c r="B251" s="3" t="s">
+      <c r="B251" s="2"/>
+      <c r="C251" s="3" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D251" s="3"/>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="2">
         <v>5835452</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B252" s="2"/>
+      <c r="C252" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D252" s="3"/>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
         <v>8613733</v>
       </c>
-      <c r="B253" s="3" t="s">
+      <c r="B253" s="2"/>
+      <c r="C253" s="3" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D253" s="3"/>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
         <v>8120142</v>
       </c>
-      <c r="B254" s="3" t="s">
+      <c r="B254" s="2"/>
+      <c r="C254" s="3" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D254" s="3"/>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
         <v>6634889</v>
       </c>
-      <c r="B255" s="3" t="s">
+      <c r="B255" s="2"/>
+      <c r="C255" s="3" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D255" s="3"/>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="2">
         <v>8324944</v>
       </c>
-      <c r="B256" s="3"/>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B256" s="2"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
         <v>6578019</v>
       </c>
-      <c r="B257" s="3" t="s">
+      <c r="B257" s="2"/>
+      <c r="C257" s="3" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D257" s="3"/>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
         <v>5546120</v>
       </c>
-      <c r="B258" s="3" t="s">
+      <c r="B258" s="2"/>
+      <c r="C258" s="3" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D258" s="3"/>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
         <v>7479297</v>
       </c>
-      <c r="B259" s="3" t="s">
+      <c r="B259" s="2"/>
+      <c r="C259" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D259" s="3"/>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="2">
         <v>5564994</v>
       </c>
-      <c r="B260" s="3" t="s">
+      <c r="B260" s="2"/>
+      <c r="C260" s="3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D260" s="3"/>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="2">
         <v>7018487</v>
       </c>
-      <c r="B261" s="3" t="s">
+      <c r="B261" s="2"/>
+      <c r="C261" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D261" s="3"/>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="2">
         <v>7018481</v>
       </c>
-      <c r="B262" s="3" t="s">
+      <c r="B262" s="2"/>
+      <c r="C262" s="3" t="s">
         <v>199</v>
       </c>
+      <c r="D262" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1048576">
+  <conditionalFormatting sqref="A1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DB.xlsx
+++ b/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sandvik-my.sharepoint.com/personal/erdogan_orhan_walter-tools_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="242" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15478A33-1293-47C6-A168-B7F00D2D1AC5}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2136E5A-ED39-44BA-9880-76986F39BF4B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1BF7449C-B9C7-49F5-BC75-D9F2737E474B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="207">
   <si>
     <t>SAP</t>
   </si>
@@ -651,6 +651,18 @@
   </si>
   <si>
     <t>YENİ ALTERNATIF</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>294682 298663 299667 299974 605018 612076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100272 294200  4530 294711 298316 298712  8721 299288 299797 299813  3777 605041 609019   609103  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100036 294502 294710  8239 298713 298758 299074  9256 602380 602474 605052  </t>
   </si>
 </sst>
 </file>
@@ -771,22 +783,7 @@
     <cellStyle name="İşaretli Hücre 2" xfId="1" xr:uid="{02D8CDB7-7CD7-467C-B70F-2ED5FD2FF432}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1069,9 +1066,9 @@
   <dimension ref="A1:D262"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="23.5546875" style="7" customWidth="1"/>
+    <col min="1" max="2" width="21.33203125" style="7" customWidth="1"/>
     <col min="3" max="3" width="203.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1104,7 +1101,9 @@
       <c r="A3" s="2">
         <v>7243868</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1114,7 +1113,9 @@
       <c r="A4" s="2">
         <v>7310123</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1124,7 +1125,9 @@
       <c r="A5" s="2">
         <v>6680174</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1134,7 +1137,9 @@
       <c r="A6" s="2">
         <v>7243904</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1144,7 +1149,9 @@
       <c r="A7" s="2">
         <v>5652820</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1154,7 +1161,9 @@
       <c r="A8" s="2">
         <v>7269368</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1164,7 +1173,9 @@
       <c r="A9" s="2">
         <v>8016825</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1174,7 +1185,9 @@
       <c r="A10" s="2">
         <v>8026019</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -1184,7 +1197,9 @@
       <c r="A11" s="2">
         <v>7425489</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1194,7 +1209,9 @@
       <c r="A12" s="2">
         <v>6907637</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
@@ -1204,7 +1221,9 @@
       <c r="A13" s="2">
         <v>6961081</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1214,7 +1233,9 @@
       <c r="A14" s="2">
         <v>7269365</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1224,15 +1245,21 @@
       <c r="A15" s="2">
         <v>6634856</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2">
+        <v>8786164</v>
+      </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>7105384</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>14</v>
       </c>
@@ -1242,7 +1269,9 @@
       <c r="A17" s="2">
         <v>6682298</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
@@ -1252,7 +1281,9 @@
       <c r="A18" s="2">
         <v>7366785</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1262,7 +1293,9 @@
       <c r="A19" s="2">
         <v>7105386</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C19" s="3" t="s">
         <v>17</v>
       </c>
@@ -1284,7 +1317,9 @@
       <c r="A21" s="2">
         <v>5834790</v>
       </c>
-      <c r="B21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
       </c>
@@ -1294,7 +1329,9 @@
       <c r="A22" s="2">
         <v>8012950</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
@@ -1304,7 +1341,9 @@
       <c r="A23" s="2">
         <v>7901960</v>
       </c>
-      <c r="B23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C23" s="3" t="s">
         <v>20</v>
       </c>
@@ -1314,7 +1353,9 @@
       <c r="A24" s="2">
         <v>5691048</v>
       </c>
-      <c r="B24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
       </c>
@@ -1324,7 +1365,9 @@
       <c r="A25" s="2">
         <v>7244726</v>
       </c>
-      <c r="B25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C25" s="3" t="s">
         <v>22</v>
       </c>
@@ -1334,7 +1377,9 @@
       <c r="A26" s="2">
         <v>6686663</v>
       </c>
-      <c r="B26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C26" s="3" t="s">
         <v>23</v>
       </c>
@@ -1344,7 +1389,9 @@
       <c r="A27" s="2">
         <v>5856728</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C27" s="3" t="s">
         <v>24</v>
       </c>
@@ -1354,7 +1401,9 @@
       <c r="A28" s="2">
         <v>7316495</v>
       </c>
-      <c r="B28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C28" s="3" t="s">
         <v>25</v>
       </c>
@@ -1364,7 +1413,9 @@
       <c r="A29" s="2">
         <v>6902777</v>
       </c>
-      <c r="B29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C29" s="3">
         <v>609018</v>
       </c>
@@ -1374,7 +1425,9 @@
       <c r="A30" s="2">
         <v>6685094</v>
       </c>
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C30" s="3" t="s">
         <v>26</v>
       </c>
@@ -1384,7 +1437,9 @@
       <c r="A31" s="2">
         <v>7275278</v>
       </c>
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C31" s="3" t="s">
         <v>27</v>
       </c>
@@ -1394,7 +1449,9 @@
       <c r="A32" s="2">
         <v>5073591</v>
       </c>
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C32" s="3" t="s">
         <v>28</v>
       </c>
@@ -1404,7 +1461,9 @@
       <c r="A33" s="2">
         <v>7269390</v>
       </c>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C33" s="3" t="s">
         <v>29</v>
       </c>
@@ -1414,15 +1473,21 @@
       <c r="A34" s="2">
         <v>6015377</v>
       </c>
-      <c r="B34" s="2"/>
+      <c r="B34" s="2">
+        <v>8214067</v>
+      </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>8214258</v>
       </c>
-      <c r="B35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C35" s="3" t="s">
         <v>30</v>
       </c>
@@ -1432,7 +1497,9 @@
       <c r="A36" s="2">
         <v>6683830</v>
       </c>
-      <c r="B36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C36" s="3" t="s">
         <v>31</v>
       </c>
@@ -1442,7 +1509,9 @@
       <c r="A37" s="2">
         <v>5834800</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C37" s="3" t="s">
         <v>32</v>
       </c>
@@ -1452,7 +1521,9 @@
       <c r="A38" s="2">
         <v>7246592</v>
       </c>
-      <c r="B38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C38" s="3" t="s">
         <v>33</v>
       </c>
@@ -1462,7 +1533,9 @@
       <c r="A39" s="2">
         <v>7242705</v>
       </c>
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C39" s="3" t="s">
         <v>34</v>
       </c>
@@ -1472,7 +1545,9 @@
       <c r="A40" s="2">
         <v>6901527</v>
       </c>
-      <c r="B40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C40" s="3" t="s">
         <v>35</v>
       </c>
@@ -1482,7 +1557,9 @@
       <c r="A41" s="2">
         <v>8016824</v>
       </c>
-      <c r="B41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C41" s="3" t="s">
         <v>36</v>
       </c>
@@ -1492,7 +1569,9 @@
       <c r="A42" s="2">
         <v>5834802</v>
       </c>
-      <c r="B42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C42" s="3" t="s">
         <v>37</v>
       </c>
@@ -1502,17 +1581,23 @@
       <c r="A43" s="2">
         <v>6015413</v>
       </c>
-      <c r="B43" s="2"/>
+      <c r="B43" s="2">
+        <v>8050481</v>
+      </c>
       <c r="C43" s="3">
         <v>393788</v>
       </c>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>6692717</v>
       </c>
-      <c r="B44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C44" s="3" t="s">
         <v>38</v>
       </c>
@@ -1522,7 +1607,9 @@
       <c r="A45" s="2">
         <v>5398789</v>
       </c>
-      <c r="B45" s="2"/>
+      <c r="B45" s="2">
+        <v>8613698</v>
+      </c>
       <c r="C45" s="3">
         <v>603144</v>
       </c>
@@ -1532,7 +1619,9 @@
       <c r="A46" s="2">
         <v>7041014</v>
       </c>
-      <c r="B46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C46" s="3" t="s">
         <v>39</v>
       </c>
@@ -1542,7 +1631,9 @@
       <c r="A47" s="2">
         <v>8186984</v>
       </c>
-      <c r="B47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C47" s="3" t="s">
         <v>40</v>
       </c>
@@ -1552,7 +1643,9 @@
       <c r="A48" s="2">
         <v>6634867</v>
       </c>
-      <c r="B48" s="2"/>
+      <c r="B48" s="2">
+        <v>8610557</v>
+      </c>
       <c r="C48" s="3">
         <v>294642</v>
       </c>
@@ -1562,7 +1655,9 @@
       <c r="A49" s="2">
         <v>6685097</v>
       </c>
-      <c r="B49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C49" s="3" t="s">
         <v>41</v>
       </c>
@@ -1572,7 +1667,9 @@
       <c r="A50" s="2">
         <v>7144515</v>
       </c>
-      <c r="B50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>42</v>
       </c>
@@ -1582,7 +1679,9 @@
       <c r="A51" s="2">
         <v>7372454</v>
       </c>
-      <c r="B51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C51" s="3" t="s">
         <v>43</v>
       </c>
@@ -1592,7 +1691,9 @@
       <c r="A52" s="2">
         <v>5337007</v>
       </c>
-      <c r="B52" s="2"/>
+      <c r="B52" s="2">
+        <v>8324924</v>
+      </c>
       <c r="C52" s="3" t="s">
         <v>44</v>
       </c>
@@ -1602,7 +1703,9 @@
       <c r="A53" s="2">
         <v>7374102</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C53" s="3" t="s">
         <v>45</v>
       </c>
@@ -1612,7 +1715,9 @@
       <c r="A54" s="2">
         <v>5398633</v>
       </c>
-      <c r="B54" s="2"/>
+      <c r="B54" s="2">
+        <v>8608208</v>
+      </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
@@ -1620,7 +1725,9 @@
       <c r="A55" s="2">
         <v>6680148</v>
       </c>
-      <c r="B55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C55" s="3" t="s">
         <v>46</v>
       </c>
@@ -1630,7 +1737,9 @@
       <c r="A56" s="2">
         <v>5850286</v>
       </c>
-      <c r="B56" s="2"/>
+      <c r="B56" s="2">
+        <v>8613777</v>
+      </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
     </row>
@@ -1638,7 +1747,9 @@
       <c r="A57" s="2">
         <v>5643787</v>
       </c>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2">
+        <v>8607463</v>
+      </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
     </row>
@@ -1646,7 +1757,9 @@
       <c r="A58" s="2">
         <v>5398751</v>
       </c>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2">
+        <v>8607874</v>
+      </c>
       <c r="C58" s="3" t="s">
         <v>47</v>
       </c>
@@ -1656,7 +1769,9 @@
       <c r="A59" s="2">
         <v>8061089</v>
       </c>
-      <c r="B59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C59" s="3" t="s">
         <v>48</v>
       </c>
@@ -1666,7 +1781,9 @@
       <c r="A60" s="2">
         <v>6686644</v>
       </c>
-      <c r="B60" s="2"/>
+      <c r="B60" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C60" s="3" t="s">
         <v>49</v>
       </c>
@@ -1676,7 +1793,9 @@
       <c r="A61" s="2">
         <v>6839957</v>
       </c>
-      <c r="B61" s="2"/>
+      <c r="B61" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C61" s="3" t="s">
         <v>50</v>
       </c>
@@ -1696,7 +1815,9 @@
       <c r="A63" s="2">
         <v>7213124</v>
       </c>
-      <c r="B63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C63" s="3" t="s">
         <v>51</v>
       </c>
@@ -1706,7 +1827,9 @@
       <c r="A64" s="2">
         <v>7246598</v>
       </c>
-      <c r="B64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C64" s="3" t="s">
         <v>52</v>
       </c>
@@ -1716,7 +1839,9 @@
       <c r="A65" s="2">
         <v>7536008</v>
       </c>
-      <c r="B65" s="2"/>
+      <c r="B65" s="2">
+        <v>8332149</v>
+      </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
     </row>
@@ -1724,7 +1849,9 @@
       <c r="A66" s="2">
         <v>5834809</v>
       </c>
-      <c r="B66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C66" s="3" t="s">
         <v>53</v>
       </c>
@@ -1734,7 +1861,9 @@
       <c r="A67" s="2">
         <v>5609163</v>
       </c>
-      <c r="B67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C67" s="3" t="s">
         <v>54</v>
       </c>
@@ -1744,7 +1873,9 @@
       <c r="A68" s="2">
         <v>5835439</v>
       </c>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2">
+        <v>8254286</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>55</v>
       </c>
@@ -1754,7 +1885,9 @@
       <c r="A69" s="2">
         <v>5874343</v>
       </c>
-      <c r="B69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C69" s="3" t="s">
         <v>56</v>
       </c>
@@ -1764,7 +1897,9 @@
       <c r="A70" s="2">
         <v>6683829</v>
       </c>
-      <c r="B70" s="2"/>
+      <c r="B70" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C70" s="3" t="s">
         <v>57</v>
       </c>
@@ -1774,7 +1909,9 @@
       <c r="A71" s="2">
         <v>6541400</v>
       </c>
-      <c r="B71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C71" s="3" t="s">
         <v>58</v>
       </c>
@@ -1784,7 +1921,9 @@
       <c r="A72" s="2">
         <v>6536188</v>
       </c>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C72" s="5" t="s">
         <v>59</v>
       </c>
@@ -1794,7 +1933,9 @@
       <c r="A73" s="2">
         <v>6972450</v>
       </c>
-      <c r="B73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C73" s="3" t="s">
         <v>60</v>
       </c>
@@ -1804,7 +1945,9 @@
       <c r="A74" s="2">
         <v>6541368</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C74" s="3" t="s">
         <v>61</v>
       </c>
@@ -1814,7 +1957,9 @@
       <c r="A75" s="2">
         <v>7316473</v>
       </c>
-      <c r="B75" s="2"/>
+      <c r="B75" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C75" s="3" t="s">
         <v>62</v>
       </c>
@@ -1824,7 +1969,9 @@
       <c r="A76" s="2">
         <v>5834792</v>
       </c>
-      <c r="B76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C76" s="3" t="s">
         <v>63</v>
       </c>
@@ -1834,7 +1981,9 @@
       <c r="A77" s="2">
         <v>7032027</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C77" s="3" t="s">
         <v>64</v>
       </c>
@@ -1844,7 +1993,9 @@
       <c r="A78" s="2">
         <v>6541367</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C78" s="3" t="s">
         <v>65</v>
       </c>
@@ -1854,7 +2005,9 @@
       <c r="A79" s="2">
         <v>6554983</v>
       </c>
-      <c r="B79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C79" s="3" t="s">
         <v>66</v>
       </c>
@@ -1864,7 +2017,9 @@
       <c r="A80" s="2">
         <v>7268757</v>
       </c>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C80" s="2" t="s">
         <v>67</v>
       </c>
@@ -1874,7 +2029,9 @@
       <c r="A81" s="2">
         <v>7246472</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C81" s="3" t="s">
         <v>68</v>
       </c>
@@ -1884,7 +2041,9 @@
       <c r="A82" s="2">
         <v>6692733</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C82" s="3" t="s">
         <v>69</v>
       </c>
@@ -1894,7 +2053,9 @@
       <c r="A83" s="2">
         <v>5915595</v>
       </c>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C83" s="3" t="s">
         <v>70</v>
       </c>
@@ -1904,7 +2065,9 @@
       <c r="A84" s="2">
         <v>6316126</v>
       </c>
-      <c r="B84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C84" s="3" t="s">
         <v>71</v>
       </c>
@@ -1914,7 +2077,9 @@
       <c r="A85" s="2">
         <v>6685095</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C85" s="4" t="s">
         <v>72</v>
       </c>
@@ -1924,7 +2089,9 @@
       <c r="A86" s="2">
         <v>6636195</v>
       </c>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C86" s="3" t="s">
         <v>73</v>
       </c>
@@ -1934,7 +2101,9 @@
       <c r="A87" s="2">
         <v>7243866</v>
       </c>
-      <c r="B87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C87" s="3" t="s">
         <v>74</v>
       </c>
@@ -1944,7 +2113,9 @@
       <c r="A88" s="2">
         <v>6636198</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C88" s="3" t="s">
         <v>75</v>
       </c>
@@ -1954,7 +2125,9 @@
       <c r="A89" s="2">
         <v>6435653</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C89" s="3" t="s">
         <v>76</v>
       </c>
@@ -1964,7 +2137,9 @@
       <c r="A90" s="2">
         <v>6574396</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C90" s="3" t="s">
         <v>77</v>
       </c>
@@ -1974,7 +2149,9 @@
       <c r="A91" s="2">
         <v>5564866</v>
       </c>
-      <c r="B91" s="2"/>
+      <c r="B91" s="2">
+        <v>8221561</v>
+      </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
     </row>
@@ -1982,7 +2159,9 @@
       <c r="A92" s="2">
         <v>5564911</v>
       </c>
-      <c r="B92" s="2"/>
+      <c r="B92" s="2">
+        <v>8221567</v>
+      </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
     </row>
@@ -1990,7 +2169,9 @@
       <c r="A93" s="2">
         <v>8221622</v>
       </c>
-      <c r="B93" s="2"/>
+      <c r="B93" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C93" s="3" t="s">
         <v>78</v>
       </c>
@@ -2000,7 +2181,9 @@
       <c r="A94" s="2">
         <v>7515113</v>
       </c>
-      <c r="B94" s="2"/>
+      <c r="B94" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C94" s="3" t="s">
         <v>79</v>
       </c>
@@ -2010,7 +2193,9 @@
       <c r="A95" s="2">
         <v>5200217</v>
       </c>
-      <c r="B95" s="2"/>
+      <c r="B95" s="2">
+        <v>8324918</v>
+      </c>
       <c r="C95" s="3" t="s">
         <v>80</v>
       </c>
@@ -2020,7 +2205,9 @@
       <c r="A96" s="2">
         <v>7684289</v>
       </c>
-      <c r="B96" s="2"/>
+      <c r="B96" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C96" s="3" t="s">
         <v>81</v>
       </c>
@@ -2030,7 +2217,9 @@
       <c r="A97" s="2">
         <v>6574415</v>
       </c>
-      <c r="B97" s="2"/>
+      <c r="B97" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C97" s="5" t="s">
         <v>82</v>
       </c>
@@ -2040,7 +2229,9 @@
       <c r="A98" s="2">
         <v>5603552</v>
       </c>
-      <c r="B98" s="2"/>
+      <c r="B98" s="2">
+        <v>8928146</v>
+      </c>
       <c r="C98" s="3" t="s">
         <v>83</v>
       </c>
@@ -2050,7 +2241,9 @@
       <c r="A99" s="2">
         <v>5564868</v>
       </c>
-      <c r="B99" s="2"/>
+      <c r="B99" s="2">
+        <v>8221564</v>
+      </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
     </row>
@@ -2058,7 +2251,9 @@
       <c r="A100" s="2">
         <v>6574417</v>
       </c>
-      <c r="B100" s="2"/>
+      <c r="B100" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C100" s="3" t="s">
         <v>84</v>
       </c>
@@ -2068,7 +2263,9 @@
       <c r="A101" s="2">
         <v>6026925</v>
       </c>
-      <c r="B101" s="2"/>
+      <c r="B101" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C101" s="3" t="s">
         <v>85</v>
       </c>
@@ -2078,7 +2275,9 @@
       <c r="A102" s="2">
         <v>6026926</v>
       </c>
-      <c r="B102" s="2"/>
+      <c r="B102" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C102" s="3" t="s">
         <v>86</v>
       </c>
@@ -2088,7 +2287,9 @@
       <c r="A103" s="2">
         <v>6054307</v>
       </c>
-      <c r="B103" s="2"/>
+      <c r="B103" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C103" s="5" t="s">
         <v>87</v>
       </c>
@@ -2098,7 +2299,9 @@
       <c r="A104" s="2">
         <v>6054279</v>
       </c>
-      <c r="B104" s="2"/>
+      <c r="B104" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C104" s="2" t="s">
         <v>88</v>
       </c>
@@ -2108,7 +2311,9 @@
       <c r="A105" s="2">
         <v>5564922</v>
       </c>
-      <c r="B105" s="2"/>
+      <c r="B105" s="2">
+        <v>8221629</v>
+      </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
     </row>
@@ -2116,7 +2321,9 @@
       <c r="A106" s="2">
         <v>5564912</v>
       </c>
-      <c r="B106" s="2"/>
+      <c r="B106" s="2">
+        <v>8221569</v>
+      </c>
       <c r="C106" s="3" t="s">
         <v>89</v>
       </c>
@@ -2126,7 +2333,9 @@
       <c r="A107" s="2">
         <v>5564919</v>
       </c>
-      <c r="B107" s="2"/>
+      <c r="B107" s="2">
+        <v>8221626</v>
+      </c>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
     </row>
@@ -2134,7 +2343,9 @@
       <c r="A108" s="2">
         <v>5932217</v>
       </c>
-      <c r="B108" s="2"/>
+      <c r="B108" s="2">
+        <v>8184778</v>
+      </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
     </row>
@@ -2142,7 +2353,9 @@
       <c r="A109" s="2">
         <v>6588365</v>
       </c>
-      <c r="B109" s="2"/>
+      <c r="B109" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C109" s="3" t="s">
         <v>90</v>
       </c>
@@ -2152,7 +2365,9 @@
       <c r="A110" s="2">
         <v>8214167</v>
       </c>
-      <c r="B110" s="2"/>
+      <c r="B110" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C110" s="3" t="s">
         <v>91</v>
       </c>
@@ -2162,7 +2377,9 @@
       <c r="A111" s="2">
         <v>6821040</v>
       </c>
-      <c r="B111" s="2"/>
+      <c r="B111" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C111" s="3">
         <v>605333</v>
       </c>
@@ -2172,7 +2389,9 @@
       <c r="A112" s="2">
         <v>6323863</v>
       </c>
-      <c r="B112" s="2"/>
+      <c r="B112" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C112" s="3" t="s">
         <v>92</v>
       </c>
@@ -2182,7 +2401,9 @@
       <c r="A113" s="2">
         <v>6792124</v>
       </c>
-      <c r="B113" s="2"/>
+      <c r="B113" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C113" s="3" t="s">
         <v>93</v>
       </c>
@@ -2192,7 +2413,9 @@
       <c r="A114" s="2">
         <v>5930639</v>
       </c>
-      <c r="B114" s="2"/>
+      <c r="B114" s="2">
+        <v>8667419</v>
+      </c>
       <c r="C114" s="3" t="s">
         <v>94</v>
       </c>
@@ -2202,7 +2425,9 @@
       <c r="A115" s="2">
         <v>5930622</v>
       </c>
-      <c r="B115" s="2"/>
+      <c r="B115" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
     </row>
@@ -2210,7 +2435,9 @@
       <c r="A116" s="2">
         <v>6313621</v>
       </c>
-      <c r="B116" s="2"/>
+      <c r="B116" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C116" s="3" t="s">
         <v>96</v>
       </c>
@@ -2220,7 +2447,9 @@
       <c r="A117" s="2">
         <v>5404935</v>
       </c>
-      <c r="B117" s="2"/>
+      <c r="B117" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C117" s="3" t="s">
         <v>97</v>
       </c>
@@ -2230,7 +2459,9 @@
       <c r="A118" s="2">
         <v>6636194</v>
       </c>
-      <c r="B118" s="2"/>
+      <c r="B118" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C118" s="5" t="s">
         <v>98</v>
       </c>
@@ -2240,7 +2471,9 @@
       <c r="A119" s="2">
         <v>6636192</v>
       </c>
-      <c r="B119" s="2"/>
+      <c r="B119" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C119" s="3" t="s">
         <v>99</v>
       </c>
@@ -2250,7 +2483,9 @@
       <c r="A120" s="2">
         <v>6819875</v>
       </c>
-      <c r="B120" s="2"/>
+      <c r="B120" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C120" s="3" t="s">
         <v>100</v>
       </c>
@@ -2260,7 +2495,9 @@
       <c r="A121" s="2">
         <v>6822509</v>
       </c>
-      <c r="B121" s="2"/>
+      <c r="B121" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C121" s="3" t="s">
         <v>101</v>
       </c>
@@ -2270,7 +2507,9 @@
       <c r="A122" s="2">
         <v>7425487</v>
       </c>
-      <c r="B122" s="2"/>
+      <c r="B122" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C122" s="3" t="s">
         <v>101</v>
       </c>
@@ -2280,7 +2519,9 @@
       <c r="A123" s="2">
         <v>5834665</v>
       </c>
-      <c r="B123" s="2"/>
+      <c r="B123" s="2">
+        <v>8325093</v>
+      </c>
       <c r="C123" s="3" t="s">
         <v>102</v>
       </c>
@@ -2290,7 +2531,9 @@
       <c r="A124" s="2">
         <v>6763436</v>
       </c>
-      <c r="B124" s="2"/>
+      <c r="B124" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C124" s="3" t="s">
         <v>103</v>
       </c>
@@ -2300,7 +2543,9 @@
       <c r="A125" s="2">
         <v>6680179</v>
       </c>
-      <c r="B125" s="2"/>
+      <c r="B125" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C125" s="3" t="s">
         <v>104</v>
       </c>
@@ -2310,7 +2555,9 @@
       <c r="A126" s="2">
         <v>6977872</v>
       </c>
-      <c r="B126" s="2"/>
+      <c r="B126" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C126" s="3" t="s">
         <v>105</v>
       </c>
@@ -2320,7 +2567,9 @@
       <c r="A127" s="2">
         <v>6962850</v>
       </c>
-      <c r="B127" s="2"/>
+      <c r="B127" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C127" s="3" t="s">
         <v>106</v>
       </c>
@@ -2330,7 +2579,9 @@
       <c r="A128" s="2">
         <v>6373052</v>
       </c>
-      <c r="B128" s="2"/>
+      <c r="B128" s="2">
+        <v>8928245</v>
+      </c>
       <c r="C128" s="3" t="s">
         <v>107</v>
       </c>
@@ -2340,7 +2591,9 @@
       <c r="A129" s="2">
         <v>7269201</v>
       </c>
-      <c r="B129" s="2"/>
+      <c r="B129" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C129" s="2" t="s">
         <v>108</v>
       </c>
@@ -2350,7 +2603,9 @@
       <c r="A130" s="2">
         <v>6026025</v>
       </c>
-      <c r="B130" s="2"/>
+      <c r="B130" s="2">
+        <v>8199129</v>
+      </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
     </row>
@@ -2358,7 +2613,9 @@
       <c r="A131" s="2">
         <v>5834099</v>
       </c>
-      <c r="B131" s="2"/>
+      <c r="B131" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C131" s="3">
         <v>605407</v>
       </c>
@@ -2368,7 +2625,9 @@
       <c r="A132" s="2">
         <v>5150521</v>
       </c>
-      <c r="B132" s="2"/>
+      <c r="B132" s="2">
+        <v>8324918</v>
+      </c>
       <c r="C132" s="3">
         <v>605410</v>
       </c>
@@ -2378,7 +2637,9 @@
       <c r="A133" s="2">
         <v>7172799</v>
       </c>
-      <c r="B133" s="2"/>
+      <c r="B133" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C133" s="3" t="s">
         <v>109</v>
       </c>
@@ -2388,7 +2649,9 @@
       <c r="A134" s="2">
         <v>6907148</v>
       </c>
-      <c r="B134" s="2"/>
+      <c r="B134" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C134" s="3" t="s">
         <v>110</v>
       </c>
@@ -2398,7 +2661,9 @@
       <c r="A135" s="2">
         <v>6432502</v>
       </c>
-      <c r="B135" s="2"/>
+      <c r="B135" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C135" s="3" t="s">
         <v>111</v>
       </c>
@@ -2408,7 +2673,9 @@
       <c r="A136" s="2">
         <v>5093169</v>
       </c>
-      <c r="B136" s="2"/>
+      <c r="B136" s="2">
+        <v>7577890</v>
+      </c>
       <c r="C136" s="3" t="s">
         <v>112</v>
       </c>
@@ -2418,7 +2685,9 @@
       <c r="A137" s="2">
         <v>6543443</v>
       </c>
-      <c r="B137" s="2"/>
+      <c r="B137" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C137" s="3" t="s">
         <v>113</v>
       </c>
@@ -2428,7 +2697,9 @@
       <c r="A138" s="2">
         <v>6682599</v>
       </c>
-      <c r="B138" s="2"/>
+      <c r="B138" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C138" s="3" t="s">
         <v>114</v>
       </c>
@@ -2438,7 +2709,9 @@
       <c r="A139" s="2">
         <v>8214176</v>
       </c>
-      <c r="B139" s="2"/>
+      <c r="B139" s="2">
+        <v>8466068</v>
+      </c>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
     </row>
@@ -2446,7 +2719,9 @@
       <c r="A140" s="2">
         <v>6960754</v>
       </c>
-      <c r="B140" s="2"/>
+      <c r="B140" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C140" s="3" t="s">
         <v>115</v>
       </c>
@@ -2456,7 +2731,9 @@
       <c r="A141" s="2">
         <v>6574414</v>
       </c>
-      <c r="B141" s="2"/>
+      <c r="B141" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C141" s="3" t="s">
         <v>116</v>
       </c>
@@ -2466,7 +2743,9 @@
       <c r="A142" s="2">
         <v>7909605</v>
       </c>
-      <c r="B142" s="2"/>
+      <c r="B142" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C142" s="3" t="s">
         <v>117</v>
       </c>
@@ -2476,7 +2755,9 @@
       <c r="A143" s="2">
         <v>7243905</v>
       </c>
-      <c r="B143" s="2"/>
+      <c r="B143" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C143" s="3" t="s">
         <v>118</v>
       </c>
@@ -2486,7 +2767,9 @@
       <c r="A144" s="2">
         <v>6819874</v>
       </c>
-      <c r="B144" s="2"/>
+      <c r="B144" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C144" s="3" t="s">
         <v>119</v>
       </c>
@@ -2496,7 +2779,9 @@
       <c r="A145" s="2">
         <v>6026028</v>
       </c>
-      <c r="B145" s="2"/>
+      <c r="B145" s="2">
+        <v>8199132</v>
+      </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
     </row>
@@ -2504,7 +2789,9 @@
       <c r="A146" s="2">
         <v>6822504</v>
       </c>
-      <c r="B146" s="2"/>
+      <c r="B146" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C146" s="3" t="s">
         <v>120</v>
       </c>
@@ -2514,7 +2801,9 @@
       <c r="A147" s="2">
         <v>7242680</v>
       </c>
-      <c r="B147" s="2"/>
+      <c r="B147" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C147" s="3" t="s">
         <v>121</v>
       </c>
@@ -2524,7 +2813,9 @@
       <c r="A148" s="2">
         <v>6745480</v>
       </c>
-      <c r="B148" s="2"/>
+      <c r="B148" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C148" s="3" t="s">
         <v>122</v>
       </c>
@@ -2534,7 +2825,9 @@
       <c r="A149" s="2">
         <v>7377485</v>
       </c>
-      <c r="B149" s="2"/>
+      <c r="B149" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C149" s="3" t="s">
         <v>123</v>
       </c>
@@ -2544,7 +2837,9 @@
       <c r="A150" s="2">
         <v>6432550</v>
       </c>
-      <c r="B150" s="2"/>
+      <c r="B150" s="2">
+        <v>6245642</v>
+      </c>
       <c r="C150" s="3" t="s">
         <v>124</v>
       </c>
@@ -2554,7 +2849,9 @@
       <c r="A151" s="2">
         <v>7559572</v>
       </c>
-      <c r="B151" s="2"/>
+      <c r="B151" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C151" s="3" t="s">
         <v>125</v>
       </c>
@@ -2564,7 +2861,9 @@
       <c r="A152" s="2">
         <v>7559571</v>
       </c>
-      <c r="B152" s="2"/>
+      <c r="B152" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C152" s="3" t="s">
         <v>126</v>
       </c>
@@ -2574,7 +2873,9 @@
       <c r="A153" s="2">
         <v>7559570</v>
       </c>
-      <c r="B153" s="2"/>
+      <c r="B153" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C153" s="3" t="s">
         <v>127</v>
       </c>
@@ -2584,7 +2885,9 @@
       <c r="A154" s="2">
         <v>5119525</v>
       </c>
-      <c r="B154" s="2"/>
+      <c r="B154" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C154" s="3" t="s">
         <v>128</v>
       </c>
@@ -2594,7 +2897,9 @@
       <c r="A155" s="2">
         <v>7389027</v>
       </c>
-      <c r="B155" s="2"/>
+      <c r="B155" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C155" s="3" t="s">
         <v>129</v>
       </c>
@@ -2604,7 +2909,9 @@
       <c r="A156" s="2">
         <v>8088591</v>
       </c>
-      <c r="B156" s="2"/>
+      <c r="B156" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C156" s="3" t="s">
         <v>130</v>
       </c>
@@ -2614,7 +2921,9 @@
       <c r="A157" s="2">
         <v>5564929</v>
       </c>
-      <c r="B157" s="2"/>
+      <c r="B157" s="2">
+        <v>8221636</v>
+      </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
     </row>
@@ -2622,7 +2931,9 @@
       <c r="A158" s="2">
         <v>5924822</v>
       </c>
-      <c r="B158" s="2"/>
+      <c r="B158" s="2">
+        <v>7377510</v>
+      </c>
       <c r="C158" s="3" t="s">
         <v>131</v>
       </c>
@@ -2632,7 +2943,9 @@
       <c r="A159" s="2">
         <v>6149840</v>
       </c>
-      <c r="B159" s="2"/>
+      <c r="B159" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C159" s="3" t="s">
         <v>132</v>
       </c>
@@ -2642,7 +2955,9 @@
       <c r="A160" s="2">
         <v>7684336</v>
       </c>
-      <c r="B160" s="2"/>
+      <c r="B160" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C160" s="3" t="s">
         <v>133</v>
       </c>
@@ -2652,7 +2967,9 @@
       <c r="A161" s="2">
         <v>5290055</v>
       </c>
-      <c r="B161" s="2"/>
+      <c r="B161" s="2">
+        <v>7310123</v>
+      </c>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
     </row>
@@ -2660,7 +2977,9 @@
       <c r="A162" s="2">
         <v>5564915</v>
       </c>
-      <c r="B162" s="2"/>
+      <c r="B162" s="2">
+        <v>8221622</v>
+      </c>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
     </row>
@@ -2668,7 +2987,9 @@
       <c r="A163" s="2">
         <v>7242681</v>
       </c>
-      <c r="B163" s="2"/>
+      <c r="B163" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C163" s="3" t="s">
         <v>134</v>
       </c>
@@ -2678,7 +2999,9 @@
       <c r="A164" s="2">
         <v>5930623</v>
       </c>
-      <c r="B164" s="2"/>
+      <c r="B164" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C164" s="3" t="s">
         <v>135</v>
       </c>
@@ -2688,7 +3011,9 @@
       <c r="A165" s="2">
         <v>8012457</v>
       </c>
-      <c r="B165" s="2"/>
+      <c r="B165" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C165" s="3" t="s">
         <v>136</v>
       </c>
@@ -2698,7 +3023,9 @@
       <c r="A166" s="2">
         <v>6245534</v>
       </c>
-      <c r="B166" s="2"/>
+      <c r="B166" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C166" s="3" t="s">
         <v>137</v>
       </c>
@@ -2708,7 +3035,9 @@
       <c r="A167" s="2">
         <v>5650559</v>
       </c>
-      <c r="B167" s="2"/>
+      <c r="B167" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
     </row>
@@ -2716,7 +3045,9 @@
       <c r="A168" s="2">
         <v>5432650</v>
       </c>
-      <c r="B168" s="2"/>
+      <c r="B168" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C168" s="3" t="s">
         <v>138</v>
       </c>
@@ -2726,7 +3057,9 @@
       <c r="A169" s="2">
         <v>6907677</v>
       </c>
-      <c r="B169" s="2"/>
+      <c r="B169" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C169" s="3" t="s">
         <v>139</v>
       </c>
@@ -2736,7 +3069,9 @@
       <c r="A170" s="2">
         <v>5649938</v>
       </c>
-      <c r="B170" s="2"/>
+      <c r="B170" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C170" s="3" t="s">
         <v>140</v>
       </c>
@@ -2746,7 +3081,9 @@
       <c r="A171" s="2">
         <v>6054309</v>
       </c>
-      <c r="B171" s="2"/>
+      <c r="B171" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C171" s="3" t="s">
         <v>141</v>
       </c>
@@ -2756,7 +3093,9 @@
       <c r="A172" s="2">
         <v>6015253</v>
       </c>
-      <c r="B172" s="2"/>
+      <c r="B172" s="2">
+        <v>8214252</v>
+      </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
     </row>
@@ -2764,7 +3103,9 @@
       <c r="A173" s="2">
         <v>6541365</v>
       </c>
-      <c r="B173" s="2"/>
+      <c r="B173" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C173" s="3" t="s">
         <v>142</v>
       </c>
@@ -2774,7 +3115,9 @@
       <c r="A174" s="2">
         <v>7310128</v>
       </c>
-      <c r="B174" s="2"/>
+      <c r="B174" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C174" s="3" t="s">
         <v>143</v>
       </c>
@@ -2784,7 +3127,9 @@
       <c r="A175" s="2">
         <v>5337002</v>
       </c>
-      <c r="B175" s="2"/>
+      <c r="B175" s="2">
+        <v>8324918</v>
+      </c>
       <c r="C175" s="3" t="s">
         <v>144</v>
       </c>
@@ -2794,7 +3139,9 @@
       <c r="A176" s="2">
         <v>5855768</v>
       </c>
-      <c r="B176" s="2"/>
+      <c r="B176" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C176" s="3" t="s">
         <v>145</v>
       </c>
@@ -2804,7 +3151,9 @@
       <c r="A177" s="2">
         <v>6541364</v>
       </c>
-      <c r="B177" s="2"/>
+      <c r="B177" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C177" s="3" t="s">
         <v>146</v>
       </c>
@@ -2814,7 +3163,9 @@
       <c r="A178" s="2">
         <v>6680172</v>
       </c>
-      <c r="B178" s="2"/>
+      <c r="B178" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C178" s="3" t="s">
         <v>147</v>
       </c>
@@ -2824,7 +3175,9 @@
       <c r="A179" s="2">
         <v>6577989</v>
       </c>
-      <c r="B179" s="2"/>
+      <c r="B179" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C179" s="3" t="s">
         <v>148</v>
       </c>
@@ -2834,7 +3187,9 @@
       <c r="A180" s="2">
         <v>7269364</v>
       </c>
-      <c r="B180" s="2"/>
+      <c r="B180" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C180" s="3" t="s">
         <v>149</v>
       </c>
@@ -2844,7 +3199,9 @@
       <c r="A181" s="2">
         <v>6907286</v>
       </c>
-      <c r="B181" s="2"/>
+      <c r="B181" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C181" s="3" t="s">
         <v>150</v>
       </c>
@@ -2854,7 +3211,9 @@
       <c r="A182" s="2">
         <v>6502447</v>
       </c>
-      <c r="B182" s="2"/>
+      <c r="B182" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C182" s="3" t="s">
         <v>151</v>
       </c>
@@ -2864,7 +3223,9 @@
       <c r="A183" s="2">
         <v>6686640</v>
       </c>
-      <c r="B183" s="2"/>
+      <c r="B183" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C183" s="3" t="s">
         <v>152</v>
       </c>
@@ -2874,7 +3235,9 @@
       <c r="A184" s="2">
         <v>5835437</v>
       </c>
-      <c r="B184" s="2"/>
+      <c r="B184" s="2">
+        <v>8254284</v>
+      </c>
       <c r="C184" s="3" t="s">
         <v>153</v>
       </c>
@@ -2884,7 +3247,9 @@
       <c r="A185" s="2">
         <v>5431642</v>
       </c>
-      <c r="B185" s="2"/>
+      <c r="B185" s="2">
+        <v>8613738</v>
+      </c>
       <c r="C185" s="3" t="s">
         <v>154</v>
       </c>
@@ -2894,7 +3259,9 @@
       <c r="A186" s="2">
         <v>6686538</v>
       </c>
-      <c r="B186" s="2"/>
+      <c r="B186" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C186" s="3" t="s">
         <v>155</v>
       </c>
@@ -2904,7 +3271,9 @@
       <c r="A187" s="2">
         <v>7941890</v>
       </c>
-      <c r="B187" s="2"/>
+      <c r="B187" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C187" s="3" t="s">
         <v>156</v>
       </c>
@@ -2914,7 +3283,9 @@
       <c r="A188" s="2">
         <v>6686561</v>
       </c>
-      <c r="B188" s="2"/>
+      <c r="B188" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C188" s="3" t="s">
         <v>157</v>
       </c>
@@ -2924,7 +3295,9 @@
       <c r="A189" s="2">
         <v>6686531</v>
       </c>
-      <c r="B189" s="2"/>
+      <c r="B189" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C189" s="3" t="s">
         <v>158</v>
       </c>
@@ -2934,7 +3307,9 @@
       <c r="A190" s="2">
         <v>8013503</v>
       </c>
-      <c r="B190" s="2"/>
+      <c r="B190" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C190" s="3" t="s">
         <v>159</v>
       </c>
@@ -2944,7 +3319,9 @@
       <c r="A191" s="2">
         <v>6323847</v>
       </c>
-      <c r="B191" s="2"/>
+      <c r="B191" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C191" s="3" t="s">
         <v>160</v>
       </c>
@@ -2954,7 +3331,9 @@
       <c r="A192" s="2">
         <v>6536180</v>
       </c>
-      <c r="B192" s="2"/>
+      <c r="B192" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C192" s="3" t="s">
         <v>161</v>
       </c>
@@ -2964,7 +3343,9 @@
       <c r="A193" s="2">
         <v>5965000</v>
       </c>
-      <c r="B193" s="2"/>
+      <c r="B193" s="2">
+        <v>8214063</v>
+      </c>
       <c r="C193" s="3" t="s">
         <v>162</v>
       </c>
@@ -2974,7 +3355,9 @@
       <c r="A194" s="2">
         <v>6846123</v>
       </c>
-      <c r="B194" s="2"/>
+      <c r="B194" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C194" s="3" t="s">
         <v>163</v>
       </c>
@@ -2984,7 +3367,9 @@
       <c r="A195" s="2">
         <v>6634853</v>
       </c>
-      <c r="B195" s="2"/>
+      <c r="B195" s="2">
+        <v>8607448</v>
+      </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
     </row>
@@ -2992,7 +3377,9 @@
       <c r="A196" s="2">
         <v>6962853</v>
       </c>
-      <c r="B196" s="2"/>
+      <c r="B196" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C196" s="3" t="s">
         <v>164</v>
       </c>
@@ -3002,7 +3389,9 @@
       <c r="A197" s="2">
         <v>6634852</v>
       </c>
-      <c r="B197" s="2"/>
+      <c r="B197" s="2">
+        <v>8608786</v>
+      </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
     </row>
@@ -3010,7 +3399,9 @@
       <c r="A198" s="2">
         <v>8199074</v>
       </c>
-      <c r="B198" s="2"/>
+      <c r="B198" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
     </row>
@@ -3018,7 +3409,9 @@
       <c r="A199" s="2">
         <v>7372458</v>
       </c>
-      <c r="B199" s="2"/>
+      <c r="B199" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C199" s="3" t="s">
         <v>165</v>
       </c>
@@ -3028,7 +3421,9 @@
       <c r="A200" s="2">
         <v>5042239</v>
       </c>
-      <c r="B200" s="2"/>
+      <c r="B200" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
     </row>
@@ -3036,7 +3431,9 @@
       <c r="A201" s="2">
         <v>5042188</v>
       </c>
-      <c r="B201" s="2"/>
+      <c r="B201" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
     </row>
@@ -3044,7 +3441,9 @@
       <c r="A202" s="2">
         <v>5042204</v>
       </c>
-      <c r="B202" s="2"/>
+      <c r="B202" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
     </row>
@@ -3052,7 +3451,9 @@
       <c r="A203" s="2">
         <v>8115583</v>
       </c>
-      <c r="B203" s="2"/>
+      <c r="B203" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
     </row>
@@ -3060,7 +3461,9 @@
       <c r="A204" s="2">
         <v>8115964</v>
       </c>
-      <c r="B204" s="2"/>
+      <c r="B204" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
     </row>
@@ -3068,7 +3471,9 @@
       <c r="A205" s="2">
         <v>8115759</v>
       </c>
-      <c r="B205" s="2"/>
+      <c r="B205" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
     </row>
@@ -3076,7 +3481,9 @@
       <c r="A206" s="2">
         <v>8115949</v>
       </c>
-      <c r="B206" s="2"/>
+      <c r="B206" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
     </row>
@@ -3084,7 +3491,9 @@
       <c r="A207" s="2">
         <v>8199067</v>
       </c>
-      <c r="B207" s="2"/>
+      <c r="B207" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C207" s="3">
         <v>603084</v>
       </c>
@@ -3094,7 +3503,9 @@
       <c r="A208" s="2">
         <v>8199070</v>
       </c>
-      <c r="B208" s="2"/>
+      <c r="B208" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
     </row>
@@ -3102,7 +3513,9 @@
       <c r="A209" s="2">
         <v>8199073</v>
       </c>
-      <c r="B209" s="2"/>
+      <c r="B209" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C209" s="3">
         <v>604132</v>
       </c>
@@ -3112,7 +3525,9 @@
       <c r="A210" s="2">
         <v>6913048</v>
       </c>
-      <c r="B210" s="2"/>
+      <c r="B210" s="2">
+        <v>8492916</v>
+      </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
     </row>
@@ -3120,7 +3535,9 @@
       <c r="A211" s="2">
         <v>8204204</v>
       </c>
-      <c r="B211" s="2"/>
+      <c r="B211" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
     </row>
@@ -3128,7 +3545,9 @@
       <c r="A212" s="2">
         <v>6791676</v>
       </c>
-      <c r="B212" s="2"/>
+      <c r="B212" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C212" s="3" t="s">
         <v>166</v>
       </c>
@@ -3138,7 +3557,9 @@
       <c r="A213" s="2">
         <v>7534743</v>
       </c>
-      <c r="B213" s="2"/>
+      <c r="B213" s="2">
+        <v>8214150</v>
+      </c>
       <c r="C213" s="3" t="s">
         <v>167</v>
       </c>
@@ -3148,7 +3569,9 @@
       <c r="A214" s="2">
         <v>8201083</v>
       </c>
-      <c r="B214" s="2"/>
+      <c r="B214" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
     </row>
@@ -3156,7 +3579,9 @@
       <c r="A215" s="2">
         <v>8296381</v>
       </c>
-      <c r="B215" s="2"/>
+      <c r="B215" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
     </row>
@@ -3164,7 +3589,9 @@
       <c r="A216" s="2">
         <v>6863847</v>
       </c>
-      <c r="B216" s="2"/>
+      <c r="B216" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
     </row>
@@ -3172,7 +3599,9 @@
       <c r="A217" s="2">
         <v>6171424</v>
       </c>
-      <c r="B217" s="2"/>
+      <c r="B217" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
     </row>
@@ -3180,7 +3609,9 @@
       <c r="A218" s="2">
         <v>7968917</v>
       </c>
-      <c r="B218" s="2"/>
+      <c r="B218" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
     </row>
@@ -3188,7 +3619,9 @@
       <c r="A219" s="2">
         <v>7969064</v>
       </c>
-      <c r="B219" s="2"/>
+      <c r="B219" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
     </row>
@@ -3196,7 +3629,9 @@
       <c r="A220" s="2">
         <v>7969106</v>
       </c>
-      <c r="B220" s="2"/>
+      <c r="B220" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
     </row>
@@ -3204,7 +3639,9 @@
       <c r="A221" s="2">
         <v>7566649</v>
       </c>
-      <c r="B221" s="2"/>
+      <c r="B221" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C221" s="3" t="s">
         <v>168</v>
       </c>
@@ -3214,7 +3651,9 @@
       <c r="A222" s="2">
         <v>7969105</v>
       </c>
-      <c r="B222" s="2"/>
+      <c r="B222" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
     </row>
@@ -3222,7 +3661,9 @@
       <c r="A223" s="2">
         <v>7169820</v>
       </c>
-      <c r="B223" s="2"/>
+      <c r="B223" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
     </row>
@@ -3230,7 +3671,9 @@
       <c r="A224" s="2">
         <v>8325013</v>
       </c>
-      <c r="B224" s="2"/>
+      <c r="B224" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
     </row>
@@ -3238,7 +3681,9 @@
       <c r="A225" s="2">
         <v>8324993</v>
       </c>
-      <c r="B225" s="2"/>
+      <c r="B225" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
     </row>
@@ -3246,7 +3691,9 @@
       <c r="A226" s="2">
         <v>7696085</v>
       </c>
-      <c r="B226" s="2"/>
+      <c r="B226" s="2">
+        <v>7696085</v>
+      </c>
       <c r="C226" s="3" t="s">
         <v>169</v>
       </c>
@@ -3256,7 +3703,9 @@
       <c r="A227" s="2">
         <v>5904483</v>
       </c>
-      <c r="B227" s="2"/>
+      <c r="B227" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C227" s="3" t="s">
         <v>170</v>
       </c>
@@ -3266,7 +3715,9 @@
       <c r="A228" s="2">
         <v>7246479</v>
       </c>
-      <c r="B228" s="2"/>
+      <c r="B228" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C228" s="3" t="s">
         <v>171</v>
       </c>
@@ -3276,7 +3727,9 @@
       <c r="A229" s="2">
         <v>5398643</v>
       </c>
-      <c r="B229" s="2"/>
+      <c r="B229" s="2">
+        <v>8928241</v>
+      </c>
       <c r="C229" s="3">
         <v>605171</v>
       </c>
@@ -3286,7 +3739,9 @@
       <c r="A230" s="2">
         <v>7246576</v>
       </c>
-      <c r="B230" s="2"/>
+      <c r="B230" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C230" s="3" t="s">
         <v>172</v>
       </c>
@@ -3296,7 +3751,9 @@
       <c r="A231" s="2">
         <v>7073348</v>
       </c>
-      <c r="B231" s="2"/>
+      <c r="B231" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C231" s="3" t="s">
         <v>173</v>
       </c>
@@ -3306,7 +3763,9 @@
       <c r="A232" s="2">
         <v>8364176</v>
       </c>
-      <c r="B232" s="2"/>
+      <c r="B232" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C232" s="3" t="s">
         <v>174</v>
       </c>
@@ -3316,7 +3775,9 @@
       <c r="A233" s="2">
         <v>6577995</v>
       </c>
-      <c r="B233" s="2"/>
+      <c r="B233" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C233" s="3" t="s">
         <v>175</v>
       </c>
@@ -3326,7 +3787,9 @@
       <c r="A234" s="2">
         <v>5398718</v>
       </c>
-      <c r="B234" s="2"/>
+      <c r="B234" s="2">
+        <v>8610024</v>
+      </c>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
     </row>
@@ -3334,7 +3797,9 @@
       <c r="A235" s="2">
         <v>8184829</v>
       </c>
-      <c r="B235" s="2"/>
+      <c r="B235" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C235" s="3" t="s">
         <v>176</v>
       </c>
@@ -3344,7 +3809,9 @@
       <c r="A236" s="2">
         <v>6808518</v>
       </c>
-      <c r="B236" s="2"/>
+      <c r="B236" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C236" s="3" t="s">
         <v>177</v>
       </c>
@@ -3354,7 +3821,9 @@
       <c r="A237" s="2">
         <v>6907673</v>
       </c>
-      <c r="B237" s="2"/>
+      <c r="B237" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C237" s="3" t="s">
         <v>178</v>
       </c>
@@ -3364,7 +3833,9 @@
       <c r="A238" s="2">
         <v>7577888</v>
       </c>
-      <c r="B238" s="2"/>
+      <c r="B238" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C238" s="3" t="s">
         <v>179</v>
       </c>
@@ -3374,7 +3845,9 @@
       <c r="A239" s="2">
         <v>6105203</v>
       </c>
-      <c r="B239" s="2"/>
+      <c r="B239" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
     </row>
@@ -3382,7 +3855,9 @@
       <c r="A240" s="2">
         <v>8026040</v>
       </c>
-      <c r="B240" s="2"/>
+      <c r="B240" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C240" s="3" t="s">
         <v>180</v>
       </c>
@@ -3392,7 +3867,9 @@
       <c r="A241" s="2">
         <v>6588369</v>
       </c>
-      <c r="B241" s="2"/>
+      <c r="B241" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C241" s="3" t="s">
         <v>181</v>
       </c>
@@ -3402,7 +3879,9 @@
       <c r="A242" s="2">
         <v>5398805</v>
       </c>
-      <c r="B242" s="2"/>
+      <c r="B242" s="2">
+        <v>8613351</v>
+      </c>
       <c r="C242" s="3" t="s">
         <v>182</v>
       </c>
@@ -3412,7 +3891,9 @@
       <c r="A243" s="2">
         <v>5932226</v>
       </c>
-      <c r="B243" s="2"/>
+      <c r="B243" s="2">
+        <v>8184787</v>
+      </c>
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
     </row>
@@ -3420,7 +3901,9 @@
       <c r="A244" s="2">
         <v>6967901</v>
       </c>
-      <c r="B244" s="2"/>
+      <c r="B244" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C244" s="3">
         <v>602745</v>
       </c>
@@ -3430,7 +3913,9 @@
       <c r="A245" s="2">
         <v>6428234</v>
       </c>
-      <c r="B245" s="2"/>
+      <c r="B245" s="2">
+        <v>8112820</v>
+      </c>
       <c r="C245" s="3" t="s">
         <v>183</v>
       </c>
@@ -3440,7 +3925,9 @@
       <c r="A246" s="2">
         <v>6680170</v>
       </c>
-      <c r="B246" s="2"/>
+      <c r="B246" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C246" s="3" t="s">
         <v>184</v>
       </c>
@@ -3450,7 +3937,9 @@
       <c r="A247" s="2">
         <v>5337020</v>
       </c>
-      <c r="B247" s="2"/>
+      <c r="B247" s="2">
+        <v>8324937</v>
+      </c>
       <c r="C247" s="3" t="s">
         <v>185</v>
       </c>
@@ -3460,7 +3949,9 @@
       <c r="A248" s="2">
         <v>7243901</v>
       </c>
-      <c r="B248" s="2"/>
+      <c r="B248" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C248" s="3" t="s">
         <v>186</v>
       </c>
@@ -3470,7 +3961,9 @@
       <c r="A249" s="2">
         <v>6577997</v>
       </c>
-      <c r="B249" s="2"/>
+      <c r="B249" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C249" s="3" t="s">
         <v>187</v>
       </c>
@@ -3480,7 +3973,9 @@
       <c r="A250" s="2">
         <v>6907269</v>
       </c>
-      <c r="B250" s="2"/>
+      <c r="B250" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C250" s="3" t="s">
         <v>188</v>
       </c>
@@ -3490,7 +3985,9 @@
       <c r="A251" s="2">
         <v>5536105</v>
       </c>
-      <c r="B251" s="2"/>
+      <c r="B251" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C251" s="3" t="s">
         <v>189</v>
       </c>
@@ -3500,7 +3997,9 @@
       <c r="A252" s="2">
         <v>5835452</v>
       </c>
-      <c r="B252" s="2"/>
+      <c r="B252" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C252" s="3" t="s">
         <v>190</v>
       </c>
@@ -3510,7 +4009,9 @@
       <c r="A253" s="2">
         <v>8613733</v>
       </c>
-      <c r="B253" s="2"/>
+      <c r="B253" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C253" s="3" t="s">
         <v>191</v>
       </c>
@@ -3520,7 +4021,9 @@
       <c r="A254" s="2">
         <v>8120142</v>
       </c>
-      <c r="B254" s="2"/>
+      <c r="B254" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C254" s="3" t="s">
         <v>192</v>
       </c>
@@ -3530,7 +4033,9 @@
       <c r="A255" s="2">
         <v>6634889</v>
       </c>
-      <c r="B255" s="2"/>
+      <c r="B255" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C255" s="3" t="s">
         <v>193</v>
       </c>
@@ -3540,7 +4045,9 @@
       <c r="A256" s="2">
         <v>8324944</v>
       </c>
-      <c r="B256" s="2"/>
+      <c r="B256" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
     </row>
@@ -3548,7 +4055,9 @@
       <c r="A257" s="2">
         <v>6578019</v>
       </c>
-      <c r="B257" s="2"/>
+      <c r="B257" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C257" s="3" t="s">
         <v>194</v>
       </c>
@@ -3558,7 +4067,9 @@
       <c r="A258" s="2">
         <v>5546120</v>
       </c>
-      <c r="B258" s="2"/>
+      <c r="B258" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C258" s="3" t="s">
         <v>195</v>
       </c>
@@ -3568,7 +4079,9 @@
       <c r="A259" s="2">
         <v>7479297</v>
       </c>
-      <c r="B259" s="2"/>
+      <c r="B259" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C259" s="3" t="s">
         <v>196</v>
       </c>
@@ -3578,7 +4091,9 @@
       <c r="A260" s="2">
         <v>5564994</v>
       </c>
-      <c r="B260" s="2"/>
+      <c r="B260" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C260" s="3" t="s">
         <v>197</v>
       </c>
@@ -3588,7 +4103,9 @@
       <c r="A261" s="2">
         <v>7018487</v>
       </c>
-      <c r="B261" s="2"/>
+      <c r="B261" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C261" s="3" t="s">
         <v>198</v>
       </c>
@@ -3598,17 +4115,15 @@
       <c r="A262" s="2">
         <v>7018481</v>
       </c>
-      <c r="B262" s="2"/>
+      <c r="B262" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C262" s="3" t="s">
         <v>199</v>
       </c>
       <c r="D262" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/DB.xlsx
+++ b/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sandvik-my.sharepoint.com/personal/erdogan_orhan_walter-tools_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2136E5A-ED39-44BA-9880-76986F39BF4B}"/>
+  <xr:revisionPtr revIDLastSave="325" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2CBCDC1-272B-48DE-B36C-EEFF627622D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1BF7449C-B9C7-49F5-BC75-D9F2737E474B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="232">
   <si>
     <t>SAP</t>
   </si>
@@ -663,6 +663,81 @@
   </si>
   <si>
     <t xml:space="preserve">100036 294502 294710  8239 298713 298758 299074  9256 602380 602474 605052  </t>
+  </si>
+  <si>
+    <t>294252 298229 299357 602911 605054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100357 294751 298323 299548 299582 602207 605057 605557 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">294715 298294 299481 393832 393901 602303 605081 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100164 294547 294816 298277 298948 299417 299418 299604 299941 393685 602024 602067 605088 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">294595 298288 299302 299676 605090 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100067 294074 299354 602413 602468 603366 604836 605100 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">294414 294527 294617 298882 605123 605163 605273 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100134 294693 298170 299824 602326 602470 602679 603273 604170 605147 612170 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100095 297001 298454 298782 298905 299558 299561 393687 393950 602930 603340 605286 605311 609076 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100046 298649 299562 299622 299661 602393 602557 602931 603047 605287 605312 605340 609063 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100171 298463 299589 299597 299653 393990 602396 602908 605303 605339 609117 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">298684 298768 299568 299569 602390 602934 603446 605319 609089 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100211 298766 299634 602483 602815 602852 602932 605322 605719 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">298491 299734 602482 605326 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100125 100126 100478 298040 602943 604040 604041 605406 605409 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">298978 299672 299675 299765 299766 602695 602705 602913 603188 603491 605683 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">298773 299585 299609 299654 602444 602933 605618 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">294173 298349 393634 393946 393986 602165 602166 602920 605004 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100028 298648 299563 299662 393587 602394 602936 605289 609083 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100034 294021 294797 298411 298710 299135 299219 393425 393661 602056 603293 605241 610085 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">602519 603186 605099 605330 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">294681 298185 299921 605408 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">602246 603255 605397 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100013 294570 298015 299297 393892 601018 604015 605701 608059 612015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">299927 602490 605723 </t>
   </si>
 </sst>
 </file>
@@ -1067,8 +1142,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="21.33203125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="203.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="203.33203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="98.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1613,7 +1688,9 @@
       <c r="C45" s="3">
         <v>603144</v>
       </c>
-      <c r="D45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
@@ -1649,7 +1726,9 @@
       <c r="C48" s="3">
         <v>294642</v>
       </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
@@ -1719,7 +1798,9 @@
         <v>8608208</v>
       </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="D54" s="3" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
@@ -1741,7 +1822,9 @@
         <v>8613777</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
@@ -1751,7 +1834,9 @@
         <v>8607463</v>
       </c>
       <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
@@ -1763,7 +1848,9 @@
       <c r="C58" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
@@ -1809,7 +1896,9 @@
         <v>8608789</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
@@ -1843,7 +1932,9 @@
         <v>8332149</v>
       </c>
       <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
@@ -2153,7 +2244,9 @@
         <v>8221561</v>
       </c>
       <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
+      <c r="D91" s="3" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
@@ -2163,7 +2256,9 @@
         <v>8221567</v>
       </c>
       <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
+      <c r="D92" s="3" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
@@ -2245,7 +2340,9 @@
         <v>8221564</v>
       </c>
       <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
+      <c r="D99" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
@@ -2315,7 +2412,9 @@
         <v>8221629</v>
       </c>
       <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
+      <c r="D105" s="3" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
@@ -2337,7 +2436,9 @@
         <v>8221626</v>
       </c>
       <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
+      <c r="D107" s="3" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
@@ -2347,7 +2448,9 @@
         <v>8184778</v>
       </c>
       <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
+      <c r="D108" s="3" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
@@ -2607,7 +2710,9 @@
         <v>8199129</v>
       </c>
       <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
+      <c r="D130" s="3" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
@@ -2783,7 +2888,9 @@
         <v>8199132</v>
       </c>
       <c r="C145" s="3"/>
-      <c r="D145" s="3"/>
+      <c r="D145" s="3" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
@@ -2925,7 +3032,9 @@
         <v>8221636</v>
       </c>
       <c r="C157" s="3"/>
-      <c r="D157" s="3"/>
+      <c r="D157" s="3" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
@@ -2971,7 +3080,9 @@
         <v>7310123</v>
       </c>
       <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
+      <c r="D161" s="3" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
@@ -2981,7 +3092,9 @@
         <v>8221622</v>
       </c>
       <c r="C162" s="3"/>
-      <c r="D162" s="3"/>
+      <c r="D162" s="3" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
@@ -3097,7 +3210,9 @@
         <v>8214252</v>
       </c>
       <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
+      <c r="D172" s="3" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
@@ -3371,7 +3486,9 @@
         <v>8607448</v>
       </c>
       <c r="C195" s="3"/>
-      <c r="D195" s="3"/>
+      <c r="D195" s="3" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
@@ -3393,7 +3510,9 @@
         <v>8608786</v>
       </c>
       <c r="C197" s="3"/>
-      <c r="D197" s="3"/>
+      <c r="D197" s="3" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
@@ -3697,7 +3816,9 @@
       <c r="C226" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D226" s="3"/>
+      <c r="D226" s="3" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
@@ -3791,7 +3912,9 @@
         <v>8610024</v>
       </c>
       <c r="C234" s="3"/>
-      <c r="D234" s="3"/>
+      <c r="D234" s="3" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
@@ -3895,7 +4018,9 @@
         <v>8184787</v>
       </c>
       <c r="C243" s="3"/>
-      <c r="D243" s="3"/>
+      <c r="D243" s="3" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="2">

--- a/DB.xlsx
+++ b/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sandvik-my.sharepoint.com/personal/erdogan_orhan_walter-tools_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="325" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2CBCDC1-272B-48DE-B36C-EEFF627622D7}"/>
+  <xr:revisionPtr revIDLastSave="329" documentId="8_{1805EA35-10FA-423C-BDD4-9975C72DA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F84CC67-A41C-453B-943F-5A84FBECBAEC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1BF7449C-B9C7-49F5-BC75-D9F2737E474B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="247">
   <si>
     <t>SAP</t>
   </si>
@@ -738,6 +738,51 @@
   </si>
   <si>
     <t xml:space="preserve">299927 602490 605723 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">294026 298328 299326 393972 605096 294026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100506 298939 602119 605669 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100170 298940 602766 605670 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">298761 299139 393666 602088 605681 608115 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">294035 298959 299525 393779 605682 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100281 298927 299771 602749 605383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100297 298986 603306 605664 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100462 298751 393991 603025 605686 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">298888 603271 605629 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100302 100303 294068 294850 298298 298308 299700 299844 602421 602422 602465 602466 603466 605086 605136 605194 605195 605363 605364 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100178 298884 298928 299247 602133 605624 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100311 298901 299931 602838 605632 609097 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100176 294870 298726 299243 602640 604631 605644 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100040 294546 294675 294890 298400 299379 605198 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100304 294587 298401 298519 299378 393921 393922 602299 605631 </t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D121BD-79E7-4CC0-A08F-DA97CDCC98A5}">
-  <dimension ref="A1:D262"/>
+  <dimension ref="A1:D278"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="21.33203125" style="7" customWidth="1"/>
@@ -4247,6 +4292,150 @@
         <v>199</v>
       </c>
       <c r="D262" s="3"/>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263" s="2">
+        <v>7243906</v>
+      </c>
+      <c r="B263" s="2"/>
+      <c r="C263" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" s="2">
+        <v>5293764</v>
+      </c>
+      <c r="B264" s="2"/>
+      <c r="C264" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" s="2">
+        <v>6795916</v>
+      </c>
+      <c r="B265" s="2"/>
+      <c r="C265" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" s="2">
+        <v>5834688</v>
+      </c>
+      <c r="B266" s="2"/>
+      <c r="C266" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" s="2">
+        <v>6432503</v>
+      </c>
+      <c r="B267" s="2"/>
+      <c r="C267" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" s="2">
+        <v>6795914</v>
+      </c>
+      <c r="B268" s="2"/>
+      <c r="C268" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269" s="2">
+        <v>7018483</v>
+      </c>
+      <c r="B269" s="2"/>
+      <c r="C269" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" s="2">
+        <v>6900620</v>
+      </c>
+      <c r="B270" s="2"/>
+      <c r="C270" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" s="2">
+        <v>8184837</v>
+      </c>
+      <c r="B271" s="2"/>
+      <c r="C271" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" s="2">
+        <v>5875410</v>
+      </c>
+      <c r="B272" s="2"/>
+      <c r="C272" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="2">
+        <v>5875410</v>
+      </c>
+      <c r="B273" s="2"/>
+      <c r="C273" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="2">
+        <v>5200215</v>
+      </c>
+      <c r="B274" s="2"/>
+      <c r="C274" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="2">
+        <v>6462172</v>
+      </c>
+      <c r="B275" s="2"/>
+      <c r="C275" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="2">
+        <v>5564999</v>
+      </c>
+      <c r="B276" s="2"/>
+      <c r="C276" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="2">
+        <v>6686535</v>
+      </c>
+      <c r="B277" s="2"/>
+      <c r="C277" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="2">
+        <v>6541366</v>
+      </c>
+      <c r="B278" s="2"/>
+      <c r="C278" s="3" t="s">
+        <v>246</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
